--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0012.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0012.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>"Chúng tôi ngắt chương trình để phát báo cáo khẩn. Mười phút trước, nhiều báo cáo về một cuộc tấn công quy mô lớn của sinh vật lạ đã xảy ra tại Khu Trung tâm Thương mại. Lực lượng An ninh Public đã thiết lập vùng cách ly và triển khai nhiều đội tìm kiếm cứu nạn. Người dân được khuyến cáo ở trong nhà, tránh xa khu vực cách ly và thực hiện các biện pháp phòng ngừa cần thiết. Những ai vẫn còn trong vùng cách ly hãy tìm nơi trú ẩn hoặc đến các điểm sơ tán được chỉ định để nhận hỗ trợ. Ngay bây giờ, chúng tôi sẽ kết nối với phóng viên tại một trong các điểm sơ tán để cập nhật thêm chi tiết về vụ tấn công."</t>
+          <t>"Chúng tôi ngắt chương trình để phát báo cáo khẩn. Mười phút trước, nhiều báo cáo về một cuộc tấn công quy mô lớn của sinh vật lạ đã xảy ra tại Khu Trung tâm Thương mại. Lực lượng An ninh Công cộng đã thiết lập vùng cách ly và triển khai nhiều đội tìm kiếm cứu nạn. Người dân được khuyến cáo ở trong nhà, tránh xa khu vực cách ly và thực hiện các biện pháp phòng ngừa cần thiết. Những ai vẫn còn trong vùng cách ly hãy tìm nơi trú ẩn hoặc đến các điểm sơ tán được chỉ định để nhận hỗ trợ. Ngay bây giờ, chúng tôi sẽ kết nối với phóng viên tại một trong các điểm sơ tán để cập nhật thêm chi tiết về vụ tấn công."</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>"Chào buổi tối. Hiện chúng ta đang đứng trước Square Midnight, với điểm sơ tán thứ hai ngay phía sau, gần hiện trường vụ tấn công kinh hoàng hôm nay nhất. Ở đây, chúng ta thấy Lực lượng An ninh Public đã thiết lập một đoàn xe vận tải lớn, tạo thành một dây chuyền sơ tán người dân..."</t>
+          <t>"Chào buổi tối. Hiện chúng ta đang đứng trước Quảng trường Midnight, với điểm sơ tán thứ hai ngay phía sau, gần hiện trường vụ tấn công kinh hoàng hôm nay nhất. Ở đây, chúng ta thấy Lực lượng An ninh Công cộng đã thiết lập một đoàn xe vận tải lớn, tạo thành một dây chuyền sơ tán người dân..."</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"...Phóng viên của chúng ta dường như đang gặp trục trặc kỹ thuật. Chúng tôi xin nhắc lại thông báo từ An ninh Public: Các công dân vẫn còn trong khu vực cách ly hãy tìm nơi trú ẩn và chờ cứu hộ, hoặc di chuyển đến các điểm sơ tán được chỉ định để nhận hỗ trợ..."</t>
+          <t>"...Phóng viên của chúng ta dường như đang gặp trục trặc kỹ thuật. Chúng tôi xin nhắc lại thông báo từ An ninh Công cộng: Các công dân vẫn còn trong khu vực cách ly hãy tìm nơi trú ẩn và chờ cứu hộ, hoặc di chuyển đến các điểm sơ tán được chỉ định để nhận hỗ trợ..."</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>"Hừ... Đừng lo, đam mê thể thao ngoài trời và tập luyện bao giờ cũng tốt mà. Cơ thể là đền thờ của cậu, phải không? Bọn trẻ bây giờ lúc nào cũng chạy theo đủ thứ, nhưng ta vẫn bảo, trước khi bon chen, hãy chăm sóc bản thân mình trước đã."</t>
+          <t>"Hừ... Đừng lo, đam mê thể thao ngoài trời và tập luyện bao giờ cũng tốt mà. Cơ thể là đền thờ của cậu, phải không? Bọn trẻ bây giờ lúc nào cũng chạy theo đủ thứ, nhưng tao vẫn bảo, trước khi bon chen, hãy chăm sóc bản thân mình trước đã."</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Đến lúc này, chiến thắng để lấy con mèo nhồi bông không còn là mục tiêu thật sự. Trò chơi đã trở thành một cuộc thử thách ý chí, một trận chiến chống lại số phận. Like truyền thuyết về người đàn ông bị kết án phải đẩy tảng đá lên núi mãi mãi, cậu không còn sợ việc món đồ chơi sẽ rơi xuống nữa.</t>
+          <t>Đến lúc này, chiến thắng để lấy con mèo nhồi bông không còn là mục tiêu thật sự. Trò chơi đã trở thành một cuộc thử thách ý chí, một trận chiến chống lại số phận. Giống như truyền thuyết về người đàn ông bị kết án phải đẩy tảng đá lên núi mãi mãi, cậu không còn sợ việc món đồ chơi sẽ rơi xuống nữa.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>"Ý cậu là cái này à? Well... Nói thật là nếu không có nó, mọi người sẽ thấy con người thật của tớ. Hay có khi tớ chỉ thấy thoải mái hơn khi nói chuyện với mọi người khi đang trốn sau nó thôi?"</t>
+          <t>"Ý cậu là cái này à? Thì... Nói thật là nếu không có nó, mọi người sẽ thấy con người thật của tớ. Hay có khi tớ chỉ thấy thoải mái hơn khi nói chuyện với mọi người khi đang trốn sau nó thôi?"</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>"Lời lẽ ngông cuồng! Bọn bay tưởng mình là ai chứ? Không có chúng ta, lũ chó biến giới như bay có đứng được đây hôm nay không? Đồ khốn, bay biết gì về danh dự? Hay chúng ta tha cho bay vì sợ hả?"</t>
+          <t>"Lời lẽ ngông cuồng! Bọn bay tưởng mình là ai chứ? Không có chúng tao, lũ chó biến giới như bay có đứng được đây hôm nay không? Đồ khốn, bay biết gì về danh dự? Hay chúng tao tha cho bay vì sợ hả?"</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>"Sự sống sót của chúng ta là nhờ Rồng Thần, chứ không phải lũ sâu bọ hèn nhát như ngươi. Còn danh dự ư? Lũ đào ngũ như ngươi không chịu nổi quái vật ở Biên giới, nên mới quay sang phản bội đồng đội à? Thử sức đi, xem chúng ta ra tay!"</t>
+          <t>"Sự sống sót của chúng ta là nhờ Rồng Thần, chứ không phải lũ sâu bọ hèn nhát như mày. Còn danh dự ư? Lũ đào ngũ như mày không chịu nổi quái vật ở Biên giới, nên mới quay sang phản bội đồng đội à? Thử sức đi, xem chúng tao ra tay!"</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>"Này, ông mặt nạ đen kia! Punch thẳng vào đi chứ?! Ôi, cẩn thận cái đĩa đó! Ta gắp cánh gà cho mà! Khôngoo, giờ nó rơi xuống đất rồi—này, đừng giẫm lên!"</t>
+          <t>"Này, ông mặt nạ đen kia! Đấm thẳng vào đi chứ?! Ôi, cẩn thận cái đĩa đó! Tao gắp cánh gà cho mà! Khôngoo, giờ nó rơi xuống đất rồi—này, đừng giẫm lên!"</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>"Tôi không sao. Cảm ơn đã giúp đỡ." Sau một thoáng im lặng, cô gái khoác áo choàng tiếp lời, "Tôi chưa từng thấy cậu bao giờ. Ngay cả trong quá khứ. Cậu không phải người vùng núi này. Vậy điều gì đưa cậu đến đây?"</t>
+          <t>"Tôi không sao. Cảm ơn cậu đã giúp đỡ." Sau một thoáng im lặng, cô gái khoác áo choàng tiếp lời, "Tôi chưa từng thấy cậu bao giờ. Ngay cả trong quá khứ. Cậu không phải người vùng núi này. Vậy điều gì đưa cậu đến đây?"</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>"Hah! Ngay cả bọn cướp còn có danh dự hơn lũ đào ngũ như các ngươi! Rồng Thần đã trở lại, và chúng ta đều biết điều đó! Mỗi mười sáu năm, nàng lại từ núi trở về. Nhưng năm nay, nàng đã biến mất hàng tháng trời mà chẳng lời nào. Vậy mà các ngươi còn dám tự xưng là dân Biên Cương?!"</t>
+          <t>"Haha! Ngay cả bọn cướp còn có danh dự hơn lũ đào ngũ như các ngươi! Rồng Thần đã trở lại, và chúng ta đều biết điều đó! Mỗi mười sáu năm, nàng lại từ núi trở về. Nhưng năm nay, nàng đã biến mất hàng tháng trời mà chẳng lời nào. Vậy mà các ngươi còn dám tự xưng là dân Biên Cương?!"</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>"Một đám ô hợp, chỉ muốn tìm Rồng trước tiên. Các người chỉ muốn lợi dụng danh tiếng của nàng để trục lợi... Pathetic. Các người đều bị chơi xỏ cả. Chẳng có Rồng Thần nào cả!"</t>
+          <t>"Một đám ô hợp, chỉ muốn tìm Rồng trước tiên. Các người chỉ muốn lợi dụng danh tiếng của nàng để trục lợi... Thảm hại. Các người đều bị chơi xỏ cả. Chẳng có Rồng Thần nào cả!"</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>"Chưa gặp cô ta bao giờ à? Nhưng ta thì gặp rồi, sau bao năm chinh chiến. Con Rồng Thần quý giá của ngươi chỉ là một con rối khác. Giống như lũ quái vật kia thôi. Cô ta cứu ngươi, nhưng chỉ vì mục đích riêng. Sự thật thực sự đang bị chôn vùi trong ngọn núi đó."</t>
+          <t>"Chưa gặp cô ta bao giờ à? Nhưng tao thì gặp rồi, sau bao năm chinh chiến. Con Rồng Thần quý giá của mày chỉ là một con rối khác. Giống như lũ quái vật kia thôi. Cô ta cứu mày, nhưng chỉ vì mục đích riêng. Sự thật thực sự đang bị chôn vùi trong ngọn núi đó."</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>"Vớ vẩn! Con rối à? Ta đang nhìn thẳng vào một con rồi đấy! Sau bao năm ở Vùng Biên Giới, sự thật còn rõ hơn ngươi tưởng! Nào, anh em. Đến lúc bịt miệng lũ nói dối đáng nguyền rủa này vĩnh viễn!"</t>
+          <t>"Vớ vẩn! Con rối à? Tao đang nhìn thẳng vào một con rồi đấy! Sau bao năm ở Vùng Biên Giới, sự thật còn rõ hơn mày tưởng! Nào, anh em. Đến lúc bịt miệng lũ nói dối đáng nguyền rủa này vĩnh viễn!"</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>"Hmm. Còn cậu thì... Ta hiểu rồi. Kể cả kế hoạch hoàn hảo nhất cũng có sơ hở. Năm nay khách đến nhiều hơn ta tưởng." Cô mỉm cười, dường như không hề bất ngờ trước sự xuất hiện của cậu.</t>
+          <t>"Hừm. Còn cậu thì... Ta hiểu rồi. Kể cả kế hoạch hoàn hảo nhất cũng có sơ hở. Năm nay khách đến nhiều hơn ta tưởng." Cô mỉm cười, dường như không hề bất ngờ trước sự xuất hiện của cậu.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>"I see... Lớn lên, ta thường nghe những câu chuyện từ các lữ khách. Họ bảo, thời thái bình, đồng ruộng trĩu hạt, ánh đèn nhà cửa lung linh trên sông."</t>
+          <t>"Ra vậy... Lớn lên, tao thường nghe những câu chuyện từ các lữ khách. Họ bảo, thời thái bình, đồng ruộng trĩu hạt, ánh đèn nhà cửa lung linh trên sông."</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>"Với Sự Rối Loạn Thời Gian đã ổn định, mối liên kết của ngọn núi với thế giới bên ngoài đã được khôi phục, và việc tiếp cận ẩm thực địa phương sẽ dễ dàng hơn. However..."</t>
+          <t>"Với Sự Rối Loạn Thời Gian đã ổn định, mối liên kết của ngọn núi với thế giới bên ngoài đã được khôi phục, và việc tiếp cận ẩm thực địa phương sẽ dễ dàng hơn. Nhưng mà..."</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>"Film à? Hành động kỳ quặc à? Có lẽ thế. Nhưng giải thích cũng chẳng thay đổi được gì. Chỉ là một giọt nước trong biển đau khổ thôi. Hy vọng đến ngày nay vẫn tồn tại chỉ nhờ vào ý chí con người."</t>
+          <t>"Phim à? Hành động kỳ quặc à? Có lẽ thế. Nhưng giải thích cũng chẳng thay đổi được gì. Chỉ là một giọt nước trong biển đau khổ thôi. Hy vọng đến ngày nay vẫn tồn tại chỉ nhờ vào ý chí con người."</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>"Ngươi luôn đặt người khác lên trước bản thân. Master từng nói 'Lập lương tâm vì trời đất. An dân định mệnh.' Nhưng ta vẫn thường tự hỏi, tại sao bản thân Thánh Long lại không được tính vào số 'dân' ấy?"</t>
+          <t>"Ngươi luôn đặt người khác lên trước bản thân. Sư phụ từng nói 'Lập lương tâm vì trời đất. An dân định mệnh.' Nhưng ta vẫn thường tự hỏi, tại sao bản thân Thánh Long lại không được tính vào số 'dân' ấy?"</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>"Đập vỡ sống lưng vảy, đốt cháy sắc hoàng hôn. Bên ngoài gương tuyết phủ, bên trong châu báu lấp lánh. Dòng nước uốn lượn lên đỉnh, đá xanh ôm lấy áo vàng. Aha! Đúng rồi! Hóa ra chúng ta là đồng môn, tiểu muội à! Nhờ ân đức của sư phụ, ta không ngờ hôm nay lại gặp được một người chị em!"</t>
+          <t>"Đập vỡ sống lưng vảy, đốt cháy sắc hoàng hôn. Bên ngoài gương tuyết phủ, bên trong châu báu lấp lánh. Dòng nước uốn lượn lên đỉnh, đá xanh ôm lấy áo vàng. A ha! Đúng rồi! Hóa ra chúng ta là đồng môn, tiểu muội à! Nhờ ân đức của sư phụ, ta không ngờ hôm nay lại gặp được một người chị em!"</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>"Nếu không phải tụi bay gây náo loạn khắp nơi thì ta cũng chẳng biết gì! Chắc biên giới này quá chật với tụi bay rồi, hả? Ai đó! Giúp với! Ta bắt được tên trộm mộ vô lại đang định bán kho báu của Thần Long đấy!"</t>
+          <t>"Nếu không phải tụi bay gây náo loạn khắp nơi thì tao cũng chẳng biết gì! Chắc biên giới này quá chật với tụi bay rồi, hả? Ai đó! Giúp với! Tao bắt được tên trộm mộ vô lại đang định bán kho báu của Thần Long đấy!"</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>"Im đi! C-Cậu có biết ở đây làm ăn kiểu gì không hả? Câm miệng lại đi! Ta có ăn cắp gì đâu! Ta còn chẳng vào nổi Đại Sảnh Loong!"</t>
+          <t>"Im đi! C-Cậu có biết ở đây làm ăn kiểu gì không hả? Câm miệng lại đi! Tao có ăn cắp gì đâu! Tao còn chẳng vào nổi Đại Sảnh Loong!"</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>"Mánh khóe gì? Các người đang cướp bóc di vật cổ đại! Ta đã gặp loại như ngươi rồi. Đồ tham tiền, lừa đảo, sẵn sàng giết người vì mấy đồng Credits... Nhanh lên! Còn giấu gì nữa không?"</t>
+          <t>"Mánh khóe gì? Các người đang cướp bóc di vật cổ đại! Tao đã gặp loại như mày rồi. Đồ tham tiền, lừa đảo, sẵn sàng giết người vì mấy đồng Credits... Nhanh lên! Còn giấu gì nữa không?"</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>"Hmph. Tưởng kiếm chác nhanh à? Được thôi. R?i ?i trước khi ngươi tè ra quần! Hôm nay ta đang hào phóng. Nhưng đừng để ta bắt gặp ngươi làm chuyện này lần nữa!"</t>
+          <t>"Hừ. Tưởng kiếm chác nhanh à? Được thôi. Cút đi trước khi mày tè ra quần! Hôm nay ta đang hào phóng. Nhưng đừng để ta bắt gặp mày làm chuyện này lần nữa!"</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>"Nếu cậu không quan tâm đến kho báu, thì lên đây làm gì? Nghe này, ta không bao giờ coi nhẹ ân huệ đâu. Nếu có gì ta có thể giúp, ta sẽ giúp!"</t>
+          <t>"Nếu cậu không quan tâm đến kho báu, thì lên đây làm gì? Nghe này, tao không bao giờ coi nhẹ ân huệ đâu. Nếu có gì tao có thể giúp, tao sẽ giúp!"</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>"That was awesome, {PlayerName}! Cảm giác như vừa ăn cả núi thức ăn dưới nước ấy! Mọi thứ ta mơ ước, còn lớn hơn cả Cetus the Tidebreaker! T-Ta… thực sự no rồi."</t>
+          <t>"Tuyệt quá, {PlayerName}! Cảm giác như vừa ăn cả núi thức ăn dưới nước ấy! Mọi thứ ta mơ ước, còn lớn hơn cả Cetus the Tidebreaker! T-Ta… thực sự no rồi."</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>"Ừ, trước đây ta chưa bao giờ hiểu điều đó, dù ở Jinzhou hay Ragunna. Nhưng giờ thì ta hiểu rồi. Mọi chuyện sẽ dễ dàng hơn nếu Vùng Biên Giới cũng thịnh vượng như Jinzhou, phải không?"</t>
+          <t>"Ừ, trước đây tao chưa bao giờ hiểu điều đó, dù ở Jinzhou hay Ragunna. Nhưng giờ thì tao hiểu rồi. Mọi chuyện sẽ dễ dàng hơn nếu Vùng Biên Giới cũng thịnh vượng như Jinzhou, phải không?"</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Cú đánh từ kẻ vô hình kia? Hay đòn chí mạng của quái vật? Dù là gì, cũng đã quá muộn để Dodge. Tim cậu đập thình thịch trong lồng ngực, như tiếng trống vô vọng chống lại số phận.</t>
+          <t>Cú đánh từ kẻ vô hình kia? Hay đòn chí mạng của quái vật? Dù là gì, cũng đã quá muộn để né tránh. Tim cậu đập thình thịch trong lồng ngực, như tiếng trống vô vọng chống lại số phận.</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Dù khung thân đã tơi tả, đôi mắt cơ khí của nó vẫn nguyên vẹn, phát sáng một màu đỏ máu thẫm. Trong ánh nhìn đó, ngươi chẳng khác gì một mảnh rác cần vứt bỏ.</t>
+          <t>Dù khung thân đã tơi tả, đôi mắt cơ khí của nó vẫn nguyên vẹn, phát sáng một màu đỏ máu thẫm. Trong ánh nhìn đó, mày chẳng khác gì một mảnh rác cần vứt bỏ.</t>
         </is>
       </c>
     </row>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>The Black Shores luôn hành động dựa trên Báo Cáo Chính Thống trước. Nhưng nếu mọi chuyện không như dự đoán, họ sẽ dựa vào Báo Cáo Ngoại Lệ để chứng minh hệ thống chưa bao giờ sai.</t>
+          <t>Bờ Biển Đen luôn hành động dựa trên Báo Cáo Chính Thống trước. Nhưng nếu mọi chuyện không như dự đoán, họ sẽ dựa vào Báo Cáo Ngoại Lệ để chứng minh hệ thống chưa bao giờ sai.</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Và bằng cách nào đó, trực giác mách bảo cậu rằng Black Shores, câu chuyện cậu vừa chứng kiến trong Somnoire, còn ẩn chứa nhiều điều hơn thế. Có lẽ nếu xem lại, một kết thúc khác sẽ hiện ra.</t>
+          <t>Và bằng cách nào đó, trực giác mách bảo cậu rằng Bờ Biển Đen, câu chuyện cậu vừa chứng kiến trong Somnoire, còn ẩn chứa nhiều điều hơn thế. Có lẽ nếu xem lại, một kết thúc khác sẽ hiện ra.</t>
         </is>
       </c>
     </row>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Not long ago, Tethys, Torrent Prescient, đã âm mưu chiếm đoạt Bờ Đen, buộc một Prescient khác phải buộc tội cậu về tội "mưu sát Prescient". Đó là lý do tại sao Bản Tin Chính Thống gán cho cậu tội danh đó.</t>
+          <t>Cách đây không lâu, Tethys, Torrent Prescient, đã âm mưu chiếm đoạt Bờ Đen, buộc một Prescient khác phải buộc tội cậu về tội "mưu sát Prescient". Đó là lý do tại sao Bản Tin Chính Thống gán cho cậu tội danh đó.</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Một ngày nọ, một lính gác kỳ cựu kể cho đám tân binh rằng Black Shores từng có một Chief Steward, người cuối cùng bị giam cầm vì âm mưu ám sát một Tiên Tri.</t>
+          <t>Một ngày nọ, một lính gác kỳ cựu kể cho đám tân binh rằng Bờ Biển Đen từng có một Quản Sự Trưởng, người cuối cùng bị giam cầm vì âm mưu ám sát một Tiên Tri.</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Ngươi thường ngước nhìn những chòm sao ảo trên Black Shores, nơi dữ liệu từ khắp nơi trên Solaris hội tụ. Hệ thống xử lý những luồng dữ liệu này thành từng cụm sao rực rỡ, rồi phóng chúng ra để tạo thành những thiên hà ảo.</t>
+          <t>Ngươi thường ngước nhìn những chòm sao ảo trên Bờ Biển Đen, nơi dữ liệu từ khắp nơi trên Solaris hội tụ. Hệ thống xử lý những luồng dữ liệu này thành từng cụm sao rực rỡ, rồi phóng chúng ra để tạo thành những thiên hà ảo.</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Không kịp Dodge. Bạn siết chặt tay cầm, chuẩn bị tinh thần.
+          <t>Không kịp né tránh. Bạn siết chặt tay cầm, chuẩn bị tinh thần.
 Cây búa giáng xuống đầu lưỡi kiếm, nghiến nát lưỡi dao như một guồng quay không ngừng. Tia lửa bắn tung, dữ dội hơn cả dòng lũ đỏ thẫm vây quanh. Bạn cảm thấy đôi tay run rẩy dữ dội, sức ép như muốn xé tan cơ thể.</t>
         </is>
       </c>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Music bắt đầu vang lên từ đâu đó. Một khúc ca của kết thúc, nhưng không hề bi thương. Nó nhẹ nhàng, tươi sáng, tràn đầy hứa hẹn.
+          <t>Âm nhạc bắt đầu vang lên từ đâu đó. Một khúc ca của kết thúc, nhưng không hề bi thương. Nó nhẹ nhàng, tươi sáng, tràn đầy hứa hẹn.
 Bằng những bước chân vững chãi, cậu quay lưng lại với hố đen đang tàn lụi và bước đi. Bởi bên kia những đổ nát ấy, là Solaris - vùng đất rộng lớn với vô vàn câu chuyện đắng cay hay ngọt ngào, và những mối liên kết vô tận đang chờ đợi được hình thành.</t>
         </is>
       </c>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>"Đi nhanh lên." Hắn bật chiếc bật lửa, ngọn lửa lơ lửng lượn lờ trong không khí." Khi chúng bắt ta phải truy tìm đường chạy của ngươi, thì coi như ngươi tiêu rồi. Chạy nhanh vào, Chief Steward."</t>
+          <t>"Đi nhanh lên." Hắn bật chiếc bật lửa, ngọn lửa lơ lửng lượn lờ trong không khí." Khi chúng bắt tao phải truy tìm đường chạy của mày, thì coi như mày tiêu rồi. Chạy nhanh vào, Quản Sự Trưởng."</t>
         </is>
       </c>
     </row>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>"Phew… Dù sao cũng cảm ơn cậu nhiều nhé! À, nhân tiện, đừng có đi đường kia đấy! Toàn là thú dữ với quái vật đáng sợ. Ta suýt chết khi đi qua đó!"</t>
+          <t>"Phù... Dù sao cũng cảm ơn cậu nhiều nhé! À, nhân tiện, đừng có đi đường kia đấy! Toàn là thú dữ với quái vật đáng sợ. Tao suýt chết khi đi qua đó!"</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>"Không sao đâu. Cậu không cần phải suy nghĩ nhiều đâu." Bạn không muốn ép cô ấy, nên thay vào đó, bạn mỉm cười và nói, "Tớ cũng có thể làm bạn của cậu không, Wooly Warrior? Tớ có thể gia nhập đội của Hoàng Tử Cosmos và Công Chúa Cloudy mà!"</t>
+          <t>"Không sao đâu. Cậu không cần phải suy nghĩ nhiều đâu." Bạn không muốn ép cô ấy, nên thay vào đó, bạn mỉm cười và nói, "Tớ cũng có thể làm bạn của cậu không, Chiến Binh Lông Xù? Tớ có thể gia nhập đội của Hoàng Tử Cosmos và Công Chúa Cloudy mà!"</t>
         </is>
       </c>
     </row>
@@ -15745,7 +15745,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Có thứ gì lấp lánh ở chỗ hắn vừa đứng. Một tấm thẻ kim loại han gỉ, khắc tên "The Hounds" bằng những Dodget chữ thô sơ, gần như man rợ. Bên dưới là một dãy mã liên lạc mờ nhạt, khó đọc.</t>
+          <t>Có thứ gì lấp lánh ở chỗ hắn vừa đứng. Một tấm thẻ kim loại han gỉ, khắc tên "The Hounds" bằng những nét chữ thô sơ, gần như man rợ. Bên dưới là một dãy mã liên lạc mờ nhạt, khó đọc.</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17359,7 @@
       <c r="M259" t="inlineStr">
         <is>
           <t>Từ ngọn lửa tím xoáy cuộn, một cô gái bước ra, nhảy múa duyên dáng giữa biển lửa.
-Váy nàng suýt chạm vào lửa mỗi khi xoay người, nhưng Dodget mặt và cử chỉ vẫn bình thản, không hề nao núng trước hiểm nguy.
+Váy nàng suýt chạm vào lửa mỗi khi xoay người, nhưng nét mặt và cử chỉ vẫn bình thản, không hề nao núng trước hiểm nguy.
 Nàng là ảo thuật gia của sân khấu, là tia sáng rực rỡ nhất của Đại Lễ Hội Thông Thái.
 Cô gái tiến lại gần cậu và cúi chào.</t>
         </is>
@@ -17430,7 +17430,7 @@
         <is>
           <t>"Ặc..." Bạn ngượng nghịu hắng giọng. Đã nhiều năm rồi không ai gọi bạn như thế.
 Ngày xưa, chính bạn đã tài trợ cho gánh xiếc.
-Khi ký ức ùa về, Dodget mặt bạn dịu lại. "Các người... đã đợi ta sao?"</t>
+Khi ký ức ùa về, nét mặt bạn dịu lại. "Các người... đã đợi ta sao?"</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
         <is>
           <t>Một tiếng ho cố ý át đi mọi âm thanh.
 Cậu dõi theo tiếng động, nhưng ánh mắt lại bị thu hút bởi chiếc lò nướng khổng lồ. Nhận ra nguồn phát ra tiếng ho ở phía bên kia nhà hàng, cậu đi vòng qua chiếc lò.
-Qua làn không khí bị méo mó vì hơi nóng, một bóng người mặc đồ trắng dần hiện ra rõ Dodget.</t>
+Qua làn không khí bị méo mó vì hơi nóng, một bóng người mặc đồ trắng dần hiện ra rõ nét.</t>
         </is>
       </c>
     </row>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>"Guest phương xa—"
+          <t>"Vị khách phương xa—"
 "Nguồn cội ta không hay—"
 "Ta muốn tựa đầu lên vai ngươi—"
 "Nhưng vầng trăng lưỡi liềm đã lặn mất rồi—"</t>
@@ -20346,7 +20346,7 @@
       <c r="M303" t="inlineStr">
         <is>
           <t>Vài nghệ sĩ đứng sẵn trên đỉnh lều xe diễu hành rạp xiếc.
-Với một cái búng tay dứt khoát của người chỉ huy, họ Dodgem những quả cầu hoa sặc sỡ lên không trung.
+Với một cái búng tay dứt khoát của người chỉ huy, họ ném những quả cầu hoa sặc sỡ lên không trung.
 Chúng bay qua quảng trường, bung ra thành những dải ruy băng rực rỡ giữa không trung. Chỉ trong nháy mắt, chúng đã phủ lên những cột đèn quanh quảng trường, nhuộm không khí đầy màu sắc và biến quảng trường trung tâm thành một sân khấu xiếc lộng lẫy.</t>
         </is>
       </c>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>"Lời ngon tiếng ngọt và tài hùng biện của {PlayerName} này! Một kẻ lừa gạt dân chúng Ragunna! Đúng là {Male=hắn;Female=cô ta} đã dùng của cải của mình làm từ thiện, và nhờ {Male=sự bảo trợ;Female=sự bảo trợ} của {Male=hắn;Female=cô ta}, Rạp Xiếc Savants đã trở thành cái tên vang xa..."</t>
+          <t>"Lời ngon tiếng ngọt và tài hùng biện của {PlayerName} này! Một kẻ lừa gạt dân chúng Ragunna! Đúng là {Male=his;Female=her} đã dùng của cải của mình làm từ thiện, và nhờ {Male=his;Female=her} của {Male=his;Female=her}, Rạp Xiếc Savants đã trở thành cái tên vang xa..."</t>
         </is>
       </c>
     </row>
@@ -21470,7 +21470,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>"Tên quý tộc của Ngân hàng Averardo này không có linh hồn! Hôm nay, chiếc thuyền gondola mà {Male=hắn;Female=bà ta} điều khiển đã chìm xuống đáy, và trong tương lai, {Male=hắn;Female=bà ta} có thể dẫn dắt dân ta đến cùng số phận!"</t>
+          <t>"Tên quý tộc của Ngân hàng Averardo này không có linh hồn! Hôm nay, chiếc thuyền gondola mà {Male=he;Female=she} điều khiển đã chìm xuống đáy, và trong tương lai, {Male=he;Female=she} có thể dẫn dắt dân ta đến cùng số phận!"</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Lúc này, chiếc Gondola mà cậu từng ngồi từ từ đứng thẳng lại. Tên nó là Shippy, em gái của Loadie quá cố. Like anh trai mình, nó đã là người bạn đồng hành trung thành của gánh xiếc suốt bao năm qua. Hai người đã diễn tập tiết mục này vô số lần.
+          <t>Lúc này, chiếc Gondola mà cậu từng ngồi từ từ đứng thẳng lại. Tên nó là Shippy, em gái của Loadie quá cố. Giống như anh trai mình, nó đã là người bạn đồng hành trung thành của gánh xiếc suốt bao năm qua. Hai người đã diễn tập tiết mục này vô số lần.
 Trong khoảnh khắc này, một làn sóng quen thuộc ập đến. Cậu biết Shippy sẽ không bao giờ quên ngày Loadie mất tích.
 Khi lấy lại thăng bằng, nó vẫy đuôi rồi khẽ cọ má vào má cậu.</t>
         </is>
@@ -21807,8 +21807,8 @@
       <c r="M325" t="inlineStr">
         <is>
           <t>"Kẻ dối trá!"
-"Ngươi tự tiện trục xuất {PlayerName} mà còn dám đứng đây ra vẻ như mình là pháp luật à! Ngươi đáng bị Dodgem ra khỏi thành phố!"
-"Ngươi mới là kẻ đứng sau cái chết của Loadie... Gia tộc Fisalia đã bị ngươi lừa gạt, đồ giả mạo!"
+"Mày tự tiện trục xuất {PlayerName} mà còn dám đứng đây ra vẻ như mình là pháp luật à! Mày đáng bị ném ra khỏi thành phố!"
+"Mày mới là kẻ đứng sau cái chết của Loadie... Gia tộc Fisalia đã bị mày lừa gạt, đồ giả mạo!"
 "{PlayerName} mới là người xứng đáng lãnh đạo Ragunna!"</t>
         </is>
       </c>
@@ -21947,7 +21947,7 @@
       <c r="M327" t="inlineStr">
         <is>
           <t>Trong tòa nhà cao cạnh quảng trường, thủ lĩnh Fisalia nhấp ly rượu. Nàng giơ ly về phía ngươi qua khung cửa sổ dài.
-Cách đó một con phố, tại văn phòng Averardo Bank, quyền giám đốc ký thỏa thuận chuyển giao với tên ngươi là người nhận.
+Cách đó một con phố, tại văn phòng Ngân Hàng Averardo, quyền giám đốc ký thỏa thuận chuyển giao với tên ngươi là người nhận.
 Bên ngoài cổng Tòa Án Mercury phía đông, một Sứ Giả Nghi Lễ đứng chờ, đón cả tội nhân lẫn một Chánh Thẩm Phán mới.
 Ngoài khơi xa, một nghệ sĩ vĩ cầm lắng nghe tiếng gầm xa xăm của đám đông, tấu lên khúc nhạc cho ngươi và cho Loadie, một bản tình ca từ ngày xưa cũ.</t>
         </is>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>"Cái gọi là Cinema Solaris này thực chất chỉ là một Quả Cầu Sonoro đặc biệt bên trong Somnoire. Một khi kết nối bị đứt và lớp bảo vệ tan biến, những thứ ẩn nấp trong bóng tối sẽ bắt đầu bò ra."</t>
+          <t>"Cái gọi là Cinema Solaris này thực chất chỉ là một Sonoro Sphere đặc biệt bên trong Somnoire. Một khi kết nối bị đứt và lớp bảo vệ tan biến, những thứ ẩn nấp trong bóng tối sẽ bắt đầu bò ra."</t>
         </is>
       </c>
     </row>
@@ -24071,7 +24071,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>"Cậu đã bao giờ thấy một Discord rời khỏi cơ thể mà vẫn để lại xác nguyên vẹn như thế này chưa? Nếu không tin lý lẽ của tôi, cứ đổ lỗi cho người thứ mười đi. Nhưng cậu không tò mò sao? Không phải cô ấy từng làm việc với người trang điểm sao?"</t>
+          <t>"Cậu đã bao giờ thấy một Tacet Discord rời khỏi cơ thể mà vẫn để lại xác nguyên vẹn như thế này chưa? Nếu không tin lý lẽ của tôi, cứ đổ lỗi cho người thứ mười đi. Nhưng cậu không tò mò sao? Không phải cô ấy từng làm việc với người trang điểm sao?"</t>
         </is>
       </c>
     </row>
@@ -24266,7 +24266,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Một luồng &lt;color=RedD&gt;lạnh giá&lt;/color&gt; bất ngờ ập đến trong Theater 2. Trong khoảnh khắc, bạn như trở lại ngọn núi tuyết phủ, đối mặt với vấn đề tương tự... Giống như cô gái trong câu chuyện ấy, *động cơ* thường ẩn sâu dưới lớp ngôn từ. Nếu chỉ nối những điểm hiển nhiên, sự thật sẽ vuột khỏi tầm tay mà không ai hay.</t>
+          <t>Một luồng &lt;color=RedD&gt;lạnh giá&lt;/color&gt; bất ngờ ập đến trong Nhà hát 2. Trong khoảnh khắc, bạn như trở lại ngọn núi tuyết phủ, đối mặt với vấn đề tương tự... Giống như cô gái trong câu chuyện ấy, *động cơ* thường ẩn sâu dưới lớp ngôn từ. Nếu chỉ nối những điểm hiển nhiên, sự thật sẽ vuột khỏi tầm tay mà không ai hay.</t>
         </is>
       </c>
     </row>
@@ -24656,7 +24656,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Dù rạp chiếu phim ngày càng bất ổn từng phút sau khi mất kết nối với Somnoire, bằng chứng lại không chỉ về một Discord ác mộng... mà là con người...</t>
+          <t>Dù rạp chiếu phim ngày càng bất ổn từng phút sau khi mất kết nối với Somnoire, bằng chứng lại không chỉ về một Tacet Discord ác mộng... mà là con người...</t>
         </is>
       </c>
     </row>
@@ -24851,7 +24851,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>"Càng bị cô lập khỏi Somnoire lâu, nơi này càng bị bóp méo bởi thứ gì đó đang trườn lên từ những tầng sâu hơn. {PlayerName} và ta đã gặp mấy con Nightmares rồi đấy."</t>
+          <t>"Càng bị cô lập khỏi Somnoire lâu, nơi này càng bị bóp méo bởi thứ gì đó đang trườn lên từ những tầng sâu hơn. {PlayerName} và tao đã gặp mấy con Ác Mộng rồi đấy."</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Nhà hát 3... Cậu nhớ lại "Report Ngoại lệ" mà hệ thống cố ém trong bộ phim thứ ba... Trong câu chuyện đó, cậu đã tin vào trực giác của mình. Cậu biết nó phải ở đó, và cuối cùng cậu đã tìm ra. Nhờ báo cáo đó, cậu giành lại được chút lợi thế từ hệ thống. Đúng là có những điều cậu không biết và không thể biết, nhưng ít nhất cậu đã nắm bắt được cơ hội trước mắt.</t>
+          <t>Nhà hát 3... Cậu nhớ lại "Báo cáo Ngoại lệ" mà hệ thống cố ém trong bộ phim thứ ba... Trong câu chuyện đó, cậu đã tin vào trực giác của mình. Cậu biết nó phải ở đó, và cuối cùng cậu đã tìm ra. Nhờ báo cáo đó, cậu giành lại được chút lợi thế từ hệ thống. Đúng là có những điều cậu không biết và không thể biết, nhưng ít nhất cậu đã nắm bắt được cơ hội trước mắt.</t>
         </is>
       </c>
     </row>
@@ -25826,7 +25826,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Nghe này, xin lỗi, nhưng giờ ta không tin ai cả... Hiện tại, hai người ngoài cuộc là đáng nghi nhất. Nói mãi về cách kẻ giết người làm thế nào, trong khi {Male=hắn;Female=cô ta} là Resonator, phải không? Ai cũng thấy cả. Nếu {Male=hắn;Female=cô ta} dùng khả năng đó, thì việc này không phải là không thể—</t>
+          <t>Nghe này, xin lỗi, nhưng giờ tao không tin ai cả... Hiện tại, hai người ngoài cuộc là đáng nghi nhất. Nói mãi về cách kẻ giết người làm thế nào, trong khi {Male=he;Female=she} là Resonator, phải không? Ai cũng thấy cả. Nếu {Male=he;Female=she} dùng khả năng đó, thì việc này không phải là không thể—</t>
         </is>
       </c>
     </row>
@@ -26671,7 +26671,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Bình chữa cháy. Chiếc bình kim loại nặng này khớp với những vết thương do lực tác động mạnh ở Theater 3. Khi kích hoạt, nó phun ra khí không cháy, và nó quá đỗi bình thường, tầm thường đến mức chẳng ai để ý đến.</t>
+          <t>Bình chữa cháy. Chiếc bình kim loại nặng này khớp với những vết thương do lực tác động mạnh ở Nhà hát 3. Khi kích hoạt, nó phun ra khí không cháy, và nó quá đỗi bình thường, tầm thường đến mức chẳng ai để ý đến.</t>
         </is>
       </c>
     </row>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Ừ... Là những người canh giữ "Cánh Cổng", Black Cat và Cat Trắng giám sát mọi tần số đi vào Somnoire. Nhưng chúng cũng nhắc rằng sâu trong Somnoire, có những vùng không thể quan sát, giống như những vùng chết của dữ liệu.</t>
+          <t>Ừ... Là những người canh giữ "Cánh Cổng", Mèo Đen và Mèo Trắng giám sát mọi tần số đi vào Somnoire. Nhưng chúng cũng nhắc rằng sâu trong Somnoire, có những vùng không thể quan sát, giống như những vùng chết của dữ liệu.</t>
         </is>
       </c>
     </row>
@@ -27451,7 +27451,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Những không gian như rạp chiếu phim này là những Quả Cầu Sonoro độc lập đã thoát khỏi sự kiểm soát của người gác cổng. Chúng vận hành theo logic riêng, là tàn tích từ thời trước khi Somnoire xuất hiện. Tethys gọi chúng là &lt;color=RedD&gt;Dư Âm của lịch sử Solaris bị hủy diệt bởi Lời Than toàn cầu&lt;/color&gt;. Dù là dấu vết mờ nhạt của những cuộc đời đã qua hay tiếng vọng ám ảnh của sự hủy diệt, chúng vẫn còn vương vấn ở đây.</t>
+          <t>Những không gian như rạp chiếu phim này là những Sonoro Sphere độc lập đã thoát khỏi sự kiểm soát của người gác cổng. Chúng vận hành theo logic riêng, là tàn tích từ thời trước khi Somnoire xuất hiện. Tethys gọi chúng là &lt;color=RedD&gt;Dư Âm của lịch sử Solaris bị hủy diệt bởi Lời Than toàn cầu&lt;/color&gt;. Dù là dấu vết mờ nhạt của những cuộc đời đã qua hay tiếng vọng ám ảnh của sự hủy diệt, chúng vẫn còn vương vấn ở đây.</t>
         </is>
       </c>
     </row>
@@ -28036,7 +28036,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Nhìn vào dòng thời gian này. Kẻ sát nhân đã hạ gục diễn viên đóng thế và nhân viên trang điểm trong lúc tìm kiếm. Rồi đến kỹ thuật viên ánh sáng ở Theater 4. Sau đó, hắn đến Nhà hát 3 để giết nhà sản xuất. Cuối cùng, hắn đổi quần áo với nạn nhân, giả làm người đó, rồi gặp lại chúng ta ở hành lang, tạo bằng chứng ngoại phạm vững chắc cho Theater 4. Nghe có đúng không?</t>
+          <t>Nhìn vào dòng thời gian này. Kẻ sát nhân đã hạ gục diễn viên đóng thế và nhân viên trang điểm trong lúc tìm kiếm. Rồi đến kỹ thuật viên ánh sáng ở Nhà hát 4. Sau đó, hắn đến Nhà hát 3 để giết nhà sản xuất. Cuối cùng, hắn đổi quần áo với nạn nhân, giả làm người đó, rồi gặp lại chúng ta ở hành lang, tạo bằng chứng ngoại phạm vững chắc cho Nhà hát 4. Nghe có đúng không?</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>"Còn về hung khí... nó luôn nằm ngay trước mắt, bên trong tủ chữa cháy tại cả ba hiện trường. Kẻ sát nhân đã dùng bình chữa cháy—vỏ kim loại nặng để đập, khí Dodgen để bóp nghẹt. Sau khi xong việc, hắn chỉ cần đặt lại chỗ cũ."</t>
+          <t>"Còn về hung khí... nó luôn nằm ngay trước mắt, bên trong tủ chữa cháy tại cả ba hiện trường. Kẻ sát nhân đã dùng bình chữa cháy—vỏ kim loại nặng để đập, khí nén để bóp nghẹt. Sau khi xong việc, hắn chỉ cần đặt lại chỗ cũ."</t>
         </is>
       </c>
     </row>
@@ -28361,7 +28361,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>"Tại sao ư? Rõ ràng mà. Rạp chiếu này bị cô lập. Stay quá lâu, nó sẽ nuốt chửng chúng ta. Cậu ở đây lâu đến nỗi... quên mất mình là ai rồi phải không?"</t>
+          <t>"Tại sao ư? Rõ ràng mà. Rạp chiếu này bị cô lập. Ở lại quá lâu, nó sẽ nuốt chửng chúng ta. Cậu ở đây lâu đến nỗi... quên mất mình là ai rồi phải không?"</t>
         </is>
       </c>
     </row>
@@ -29011,7 +29011,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>"Đúng là dấu vết dẫn đến một 'kẻ sát nhân' trong rạp chiếu phim này. Nhưng ta muốn biết... tại sao cái rạp này lại tồn tại? Vội vàng kết thúc vụ án và gán cho nó một lời giải thích tiện lợi có thật sự đưa chúng ta đến sự thật không?"</t>
+          <t>"Đúng là dấu vết dẫn đến một 'kẻ sát nhân' trong rạp chiếu phim này. Nhưng tao muốn biết... tại sao cái rạp này lại tồn tại? Vội vàng kết thúc vụ án và gán cho nó một lời giải thích tiện lợi có thật sự đưa chúng ta đến sự thật không?"</t>
         </is>
       </c>
     </row>
@@ -29141,7 +29141,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>"Cậu đã chiến đấu đủ lâu rồi. Giờ mọi chuyện đã kết thúc. Cậu đã làm rất tốt. Phần còn lại hãy để chúng tôi lo. Chúng tôi sẽ lưu giữ câu chuyện của cậu trong một giấc mơ. Dù quê hương có mất đi, dù dân tộc có biến mất, dù lời nói và lịch sử có phai mờ... thì đến tận cùng thời gian, giấc mơ vẫn sẽ còn đó." Đó là lời hứa của Black Cat.</t>
+          <t>"Cậu đã chiến đấu đủ lâu rồi. Giờ mọi chuyện đã kết thúc. Cậu đã làm rất tốt. Phần còn lại hãy để chúng tôi lo. Chúng tôi sẽ lưu giữ câu chuyện của cậu trong một giấc mơ. Dù quê hương có mất đi, dù dân tộc có biến mất, dù lời nói và lịch sử có phai mờ... thì đến tận cùng thời gian, giấc mơ vẫn sẽ còn đó." Đó là lời hứa của Mèo Đen.</t>
         </is>
       </c>
     </row>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>"Bị ràng buộc bởi lời hứa với người tạo ra mình, Black Cat và Cat Trắng buộc phải phân mảnh thế giới giấc mơ thành từng tầng riêng biệt, cắt đứt từng lớp một, thậm chí xóa bỏ chính bản thân cùng những giấc mơ ô uế, tất cả chỉ để phong ấn *Nó* vào tầng sâu nhất."</t>
+          <t>"Bị ràng buộc bởi lời hứa với người tạo ra mình, Mèo Đen và Mèo Trắng buộc phải phân mảnh thế giới giấc mơ thành từng tầng riêng biệt, cắt đứt từng lớp một, thậm chí xóa bỏ chính bản thân cùng những giấc mơ ô uế, tất cả chỉ để phong ấn *Nó* vào tầng sâu nhất."</t>
         </is>
       </c>
     </row>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>"Thời gian trôi qua. Tái sinh như cũ, lũ mèo vẫn tuân theo ý chỉ của người tạo ra chúng, lang thang ở những tầng trên để thu thập những giấc mơ đang phai nhạt của thế giới. Cho đến một ngày, đống giấc mơ chất chứa ấy thấm xuống vương quốc dưới nước. Vào khoảnh khắc đó, chúng cảm nhận được một sự xao động từ tầng sâu nhất. Một lần nữa, Black Cat và Cat Trắng lại đứng chia đôi—"</t>
+          <t>"Thời gian trôi qua. Tái sinh như cũ, lũ mèo vẫn tuân theo ý chỉ của người tạo ra chúng, lang thang ở những tầng trên để thu thập những giấc mơ đang phai nhạt của thế giới. Cho đến một ngày, đống giấc mơ chất chứa ấy thấm xuống vương quốc dưới nước. Vào khoảnh khắc đó, chúng cảm nhận được một sự xao động từ tầng sâu nhất. Một lần nữa, Mèo Đen và Mèo Trắng lại đứng chia đôi—"</t>
         </is>
       </c>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>"Nhưng có một điều cậu hiểu nhầm rồi... Rạp chiếu phim này không phải là thứ duy nhất ta sở hữu. &lt;color=RedD&gt;Toàn bộ tầng Somnoire&lt;/color&gt; mà cậu đang đứng này đều là của ta. Cái gọi là rạp chiếu phim này chỉ là một nấm mồ bị lãng quên. Còn những thước phim trưng bày ở đây? Gọi chúng là cách giết thời gian... hay có khi là món quà chào mừng nhỏ, chỉ dành riêng cho cậu thôi."</t>
+          <t>"Nhưng có một điều cậu hiểu nhầm rồi... Rạp chiếu phim này không phải là thứ duy nhất tao sở hữu. &lt;color=RedD&gt;Toàn bộ tầng Somnoire&lt;/color&gt; mà cậu đang đứng này đều là của tao. Cái gọi là rạp chiếu phim này chỉ là một nấm mồ bị lãng quên. Còn những thước phim trưng bày ở đây? Gọi chúng là cách giết thời gian... hay có khi là món quà chào mừng nhỏ, chỉ dành riêng cho cậu thôi."</t>
         </is>
       </c>
     </row>
@@ -30701,7 +30701,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>"Hmm... Let me think. Giống như trong những câu chuyện trinh thám ấy, thám tử thiên tài luôn phải đối đầu với một tên tội phạm cũng thiên tài không kém, phải không? Nhưng nếu thám tử bắt được kẻ xấu quá sớm, hay kẻ xấu hạ gục anh hùng trước khi câu chuyện bắt đầu... thì đúng là chán ngắt."</t>
+          <t>"Hừm... Để ta nghĩ xem. Giống như trong những câu chuyện trinh thám ấy, thám tử thiên tài luôn phải đối đầu với một tên tội phạm cũng thiên tài không kém, phải không? Nhưng nếu thám tử bắt được kẻ xấu quá sớm, hay kẻ xấu hạ gục anh hùng trước khi câu chuyện bắt đầu... thì đúng là chán ngắt."</t>
         </is>
       </c>
     </row>
@@ -30766,7 +30766,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>"Chuẩn luôn! Đây còn lâu mới phải vụ án cuối cùng. Mũ nồi của ta cậu vẫn giữ chứ? Giữ nó cẩn thận nhé. Từ giờ, nó là huy hiệu của một thám tử tài ba đấy. Mang nó về thế giới của cậu, tìm thêm cảm hứng cho những bộ phim của ta... Như vậy, lần sau cậu quay lại tìm ta, những câu đố của ta sẽ còn hấp dẫn hơn nữa."</t>
+          <t>"Chuẩn luôn! Đây còn lâu mới phải vụ án cuối cùng. Mũ nồi của tao cậu vẫn giữ chứ? Giữ nó cẩn thận nhé. Từ giờ, nó là huy hiệu của một thám tử tài ba đấy. Mang nó về thế giới của cậu, tìm thêm cảm hứng cho những bộ phim của tao... Như vậy, lần sau cậu quay lại tìm tao, những câu đố của tao sẽ còn hấp dẫn hơn nữa."</t>
         </is>
       </c>
     </row>
@@ -30896,7 +30896,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>"Lý luận của kẻ sát nhân rất đơn giản. Like *Nó* nghĩ rằng người chết không thể nói, nên *Nó* đã hủy diệt mọi thứ có hình hài, tin rằng sự thật có thể bị chôn vùi bằng cách đặt lại mọi thứ về con số không. Nhưng thám tử thì khác. Những gì tồn tại đều để lại dấu vết, nên thám tử không bao giờ dừng lại. Chừng nào còn sự thật cần khám phá, sẽ luôn có bằng chứng."</t>
+          <t>"Lý luận của kẻ sát nhân rất đơn giản. Giống như *Nó* nghĩ rằng người chết không thể nói, nên *Nó* đã hủy diệt mọi thứ có hình hài, tin rằng sự thật có thể bị chôn vùi bằng cách đặt lại mọi thứ về con số không. Nhưng thám tử thì khác. Những gì tồn tại đều để lại dấu vết, nên thám tử không bao giờ dừng lại. Chừng nào còn sự thật cần khám phá, sẽ luôn có bằng chứng."</t>
         </is>
       </c>
     </row>
@@ -30961,7 +30961,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Đó là... không gian đang sụp đổ sao? Dưới kia, đám đông ngửa cổ, mắt dán chặt lên bầu trời khi màn đêm từ từ hạ xuống với tốc độ có thể nhìn thấy. Những ánh sao xa xôi từ những đốm lửa cổ xưa đã tắt từ lâu bị kéo vào trong, Dodgen lại thành một dải sáng rực do hiệu ứng co cụm, để lại vệt lửa trắng như minh chứng cho ảnh hưởng của dịch chuyển xanh.</t>
+          <t>Đó là... không gian đang sụp đổ sao? Dưới kia, đám đông ngửa cổ, mắt dán chặt lên bầu trời khi màn đêm từ từ hạ xuống với tốc độ có thể nhìn thấy. Những ánh sao xa xôi từ những đốm lửa cổ xưa đã tắt từ lâu bị kéo vào trong, nén lại thành một dải sáng rực do hiệu ứng co cụm, để lại vệt lửa trắng như minh chứng cho ảnh hưởng của dịch chuyển xanh.</t>
         </is>
       </c>
     </row>
@@ -31416,7 +31416,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>"Tiến triển à? Not a chance. Ánh sáng đó chỉ tồn tại chưa đầy một giây trong năm nay. Việc máy thu của chúng ta phát hiện được nó năm lần liên tiếp đã là một phép màu rồi."</t>
+          <t>"Tiến triển à? Không đời nào. Ánh sáng đó chỉ tồn tại chưa đầy một giây trong năm nay. Việc máy thu của chúng ta phát hiện được nó năm lần liên tiếp đã là một phép màu rồi."</t>
         </is>
       </c>
     </row>
@@ -31546,7 +31546,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>"Bởi vì tớ không thể... Thật ra, năm ngoái chúng tớ đã tiến hành thí nghiệm trên luồng ánh sáng đó. Hầu hết kết quả đều cho thấy những xung một giây đó chứa một lượng thông tin khổng lồ. Dựa trên phân tích phân bố tần số... mức entropy của ngôn ngữ trong những xung đó khoảng... 30. Khoan, sao mặt cậu thế? Cậu có biết entropy ngôn ngữ là gì không?"</t>
+          <t>"Bởi vì tớ không thể... Thật ra, năm ngoái chúng tớ đã tiến hành thí nghiệm trên luồng ánh sáng đó. Hầu hết kết quả đều cho thấy những xung một giây đó chứa một lượng thông tin khổng lồ. Dựa trên phân tích phân bố tần số... mức entropy của ngôn ngữ trong những xung đó khoảng... 30. Đợi đã, sao mặt cậu thế? Cậu có biết entropy ngôn ngữ là gì không?"</t>
         </is>
       </c>
     </row>
@@ -31936,7 +31936,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>"Cậu đã nghe qua Paradox Swampman chưa? Một tia sét đánh trúng một người, thiêu rụi họ hoàn toàn. Nhưng trùng hợp thay, tia sét đó đồng thời kích hoạt một phản ứng kỳ lạ trong đầm lầy gần đó, tạo ra một sinh vật giống hệt người ban đầu về mọi mặt—"</t>
+          <t>"Cậu đã nghe qua Nghịch Lý Swampman chưa? Một tia sét đánh trúng một người, thiêu rụi họ hoàn toàn. Nhưng trùng hợp thay, tia sét đó đồng thời kích hoạt một phản ứng kỳ lạ trong đầm lầy gần đó, tạo ra một sinh vật giống hệt người ban đầu về mọi mặt—"</t>
         </is>
       </c>
     </row>
@@ -32261,7 +32261,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>"Not really. Cuộc sống ở mỗi giai đoạn cũng na ná như nhau thôi. Có khác biệt nhỏ, nhưng chẳng có gì đáng để bận tâm cả. Tin tôi đi, càng sống lâu trên đời này, cậu sẽ càng thấy rõ. Sự bực bội này chẳng bao giờ chấm dứt. Con người luôn lo lắng về điều gì đó, từ khi sinh ra cho đến lúc nhắm mắt. Cậu nghĩ chuyển sang giai đoạn mới hay thay đổi môi trường sẽ khá hơn à? Chẳng thay đổi gì đâu."</t>
+          <t>"Không hẳn. Cuộc sống ở mỗi giai đoạn cũng na ná như nhau thôi. Có khác biệt nhỏ, nhưng chẳng có gì đáng để bận tâm cả. Tin tôi đi, càng sống lâu trên đời này, cậu sẽ càng thấy rõ. Sự bực bội này chẳng bao giờ chấm dứt. Con người luôn lo lắng về điều gì đó, từ khi sinh ra cho đến lúc nhắm mắt. Cậu nghĩ chuyển sang giai đoạn mới hay thay đổi môi trường sẽ khá hơn à? Chẳng thay đổi gì đâu."</t>
         </is>
       </c>
     </row>
@@ -32391,7 +32391,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>"Để xem con yak lăn. Nghe nói đoàn xiếc mới có một con. Nó chỉ ngồi lì cả ngày. Có khi vì khán giả cứ chọc que vào nó, hay đơn giản là nó thích ngồi thế. Mọi người từ khắp nơi kéo đến xem, Dodgem đồ ăn vào nó, nhưng nó chẳng phản ứng gì. Vẫn ngồi im, thậm chí gió thổi cũng không lăn. Ngày nào cũng vậy, chẳng làm gì cả."</t>
+          <t>"Để xem con yak lăn. Nghe nói đoàn xiếc mới có một con. Nó chỉ ngồi lì cả ngày. Có khi vì khán giả cứ chọc que vào nó, hay đơn giản là nó thích ngồi thế. Mọi người từ khắp nơi kéo đến xem, ném đồ ăn vào nó, nhưng nó chẳng phản ứng gì. Vẫn ngồi im, thậm chí gió thổi cũng không lăn. Ngày nào cũng vậy, chẳng làm gì cả."</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>"Nếu ta hỏi ngươi về việc đo lường những đại lượng vật lý đó bằng khoa học, chắc ngươi sẽ Dodgem cho ta một đống lý thuyết phòng thí nghiệm tiên tiến, nói về nguyên lý cộng hưởng và công thức giãn nở phức tạp, tinh tế và chính xác đến thế nào. Ừ, đúng là vậy. Nhưng ngươi chưa bao giờ chứng kiến một phát minh đột phá lan tỏa khắp thế giới, từng chút một, cho đến khi chẳng còn gì là cũ kỹ nữa. Ngươi không biết cảm giác thế nào khi thấy một bước nhảy vọt công nghệ xóa sổ tất cả những gì đã có trước đó."</t>
+          <t>"Nếu tao hỏi mày về việc đo lường những đại lượng vật lý đó bằng khoa học, chắc mày sẽ ném cho tao một đống lý thuyết phòng thí nghiệm tiên tiến, nói về nguyên lý cộng hưởng và công thức giãn nở phức tạp, tinh tế và chính xác đến thế nào. Ừ, đúng là vậy. Nhưng mày chưa bao giờ chứng kiến một phát minh đột phá lan tỏa khắp thế giới, từng chút một, cho đến khi chẳng còn gì là cũ kỹ nữa. Mày không biết cảm giác thế nào khi thấy một bước nhảy vọt công nghệ xóa sổ tất cả những gì đã có trước đó."</t>
         </is>
       </c>
     </row>
@@ -33106,7 +33106,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>"Thôi đi, đùa à! Đến giờ mới nói với ta? Không có luật lệ gì à? Lần đầu trúng là ăn may, lần hai là trùng hợp, nhưng lần ba? Không đời nào ta thắng được nữa... Khoan đã, họ tự chọn số hay để máy chọn?"</t>
+          <t>"Thôi đi, đùa à! Đến giờ mới nói với tao? Không có luật lệ gì à? Lần đầu trúng là ăn may, lần hai là trùng hợp, nhưng lần ba? Không đời nào tao thắng được nữa... Khoan đã, họ tự chọn số hay để máy chọn?"</t>
         </is>
       </c>
     </row>
